--- a/assets/inventory/excel/רשימת_מכנסיים.xlsx
+++ b/assets/inventory/excel/רשימת_מכנסיים.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldad-my.sharepoint.com/personal/nave_reouel_com/Documents/מסמכים/פיתוח/hightide/assets/inventory/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_D59710881FE11F9269A083521B532902419DE227" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BECB5A1-81A6-4305-8EEB-65483E6BF47A}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="2184" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="1960" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="רשימת מכנסיים" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -188,7 +187,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -490,12 +489,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PantsTable" displayName="PantsTable" ref="A3:D30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D30">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="מספר מכנס"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="שם מכנס"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="מידה"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="תאריך" dataDxfId="0">
+    <tableColumn id="1" name="מספר מכנס"/>
+    <tableColumn id="2" name="שם מכנס"/>
+    <tableColumn id="3" name="מידה"/>
+    <tableColumn id="4" name="תאריך" dataDxfId="0">
       <calculatedColumnFormula>$K$2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -651,19 +650,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="12.59765625" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.58203125" customWidth="1"/>
+    <col min="6" max="6" width="9.9140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
@@ -681,7 +680,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.2" customHeight="1" thickTop="1">
+    <row r="3" spans="1:11" ht="19.25" customHeight="1" thickTop="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -701,7 +700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.8" customHeight="1">
+    <row r="4" spans="1:11" ht="16.75" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
@@ -725,7 +724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.8" customHeight="1">
+    <row r="5" spans="1:11" ht="16.75" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -739,9 +738,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E5" s="19" t="str">
-        <f>$E$4</f>
-        <v>לא נמכר</v>
+      <c r="E5" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="22">
         <v>250</v>
@@ -750,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.8" customHeight="1">
+    <row r="6" spans="1:11" ht="16.75" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
@@ -774,7 +772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.8" customHeight="1">
+    <row r="7" spans="1:11" ht="16.75" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -796,7 +794,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.8" customHeight="1">
+    <row r="8" spans="1:11" ht="16.75" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -817,7 +815,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.8" customHeight="1">
+    <row r="9" spans="1:11" ht="16.75" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
@@ -839,7 +837,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.8" customHeight="1">
+    <row r="10" spans="1:11" ht="16.75" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
@@ -853,15 +851,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E10" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E10" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F10" s="21">
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.8" customHeight="1">
+    <row r="11" spans="1:11" ht="16.75" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
@@ -876,13 +873,13 @@
         <v>46217</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" s="22">
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.8" customHeight="1">
+    <row r="12" spans="1:11" ht="16.75" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
@@ -904,7 +901,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.8" customHeight="1">
+    <row r="13" spans="1:11" ht="16.75" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
@@ -926,7 +923,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.8" customHeight="1">
+    <row r="14" spans="1:11" ht="16.75" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
@@ -948,7 +945,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.8" customHeight="1">
+    <row r="15" spans="1:11" ht="16.75" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -962,15 +959,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E15" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E15" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="22">
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.8" customHeight="1">
+    <row r="16" spans="1:11" ht="16.75" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>31</v>
       </c>
@@ -984,15 +980,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E16" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E16" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="21">
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16.8" customHeight="1">
+    <row r="17" spans="1:6" ht="16.75" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
@@ -1014,7 +1009,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16.8" customHeight="1">
+    <row r="18" spans="1:6" ht="16.75" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -1028,15 +1023,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E18" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E18" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="21">
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16.8" customHeight="1">
+    <row r="19" spans="1:6" ht="16.75" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
@@ -1058,7 +1052,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16.8" customHeight="1">
+    <row r="20" spans="1:6" ht="16.75" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
@@ -1080,7 +1074,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16.8" customHeight="1">
+    <row r="21" spans="1:6" ht="16.75" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>37</v>
       </c>
@@ -1102,7 +1096,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16.8" customHeight="1">
+    <row r="22" spans="1:6" ht="16.75" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
@@ -1124,7 +1118,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16.8" customHeight="1">
+    <row r="23" spans="1:6" ht="16.75" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
@@ -1138,15 +1132,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E23" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E23" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F23" s="22">
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16.8" customHeight="1">
+    <row r="24" spans="1:6" ht="16.75" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>40</v>
       </c>
@@ -1160,15 +1153,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E24" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E24" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F24" s="21">
         <v>250</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="16.8" customHeight="1">
+    <row r="25" spans="1:6" ht="16.75" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>41</v>
       </c>
@@ -1190,7 +1182,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16.8" customHeight="1">
+    <row r="26" spans="1:6" ht="16.75" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>43</v>
       </c>
@@ -1204,15 +1196,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E26" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E26" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F26" s="21">
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.8" customHeight="1">
+    <row r="27" spans="1:6" ht="16.75" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>45</v>
       </c>
@@ -1234,7 +1225,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16.8" customHeight="1">
+    <row r="28" spans="1:6" ht="16.75" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>47</v>
       </c>
@@ -1256,7 +1247,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16.8" customHeight="1">
+    <row r="29" spans="1:6" ht="16.75" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>48</v>
       </c>
@@ -1278,7 +1269,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16.8" customHeight="1">
+    <row r="30" spans="1:6" ht="16.75" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
@@ -1305,7 +1296,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30">
       <formula1>$K$5:$K$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/inventory/excel/רשימת_מכנסיים.xlsx
+++ b/assets/inventory/excel/רשימת_מכנסיים.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -1110,9 +1110,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E22" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E22" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F22" s="21">
         <v>260</v>

--- a/assets/inventory/excel/רשימת_מכנסיים.xlsx
+++ b/assets/inventory/excel/רשימת_מכנסיים.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\נווה\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAE7371-CF38-45C2-9060-1B0D1B87B52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="1960" windowHeight="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="רשימת מכנסיים" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -187,7 +188,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -489,12 +490,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PantsTable" displayName="PantsTable" ref="A3:D30">
   <tableColumns count="4">
-    <tableColumn id="1" name="מספר מכנס"/>
-    <tableColumn id="2" name="שם מכנס"/>
-    <tableColumn id="3" name="מידה"/>
-    <tableColumn id="4" name="תאריך" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="מספר מכנס"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="שם מכנס"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="מידה"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="תאריך" dataDxfId="0">
       <calculatedColumnFormula>$K$2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -650,19 +651,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="12.58203125" customWidth="1"/>
-    <col min="6" max="6" width="9.9140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.59765625" customWidth="1"/>
+    <col min="6" max="6" width="9.8984375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
@@ -680,7 +681,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.25" customHeight="1" thickTop="1">
+    <row r="3" spans="1:11" ht="19.2" customHeight="1" thickTop="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -700,7 +701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.75" customHeight="1">
+    <row r="4" spans="1:11" ht="16.8" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
@@ -715,7 +716,7 @@
         <v>46217</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" s="21">
         <v>250</v>
@@ -724,7 +725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.75" customHeight="1">
+    <row r="5" spans="1:11" ht="16.8" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -748,7 +749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.75" customHeight="1">
+    <row r="6" spans="1:11" ht="16.8" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
@@ -772,7 +773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.75" customHeight="1">
+    <row r="7" spans="1:11" ht="16.8" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -786,15 +787,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E7" s="19" t="str">
-        <f>$E$4</f>
-        <v>לא נמכר</v>
+      <c r="E7" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F7" s="22">
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.75" customHeight="1">
+    <row r="8" spans="1:11" ht="16.8" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -815,7 +815,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.75" customHeight="1">
+    <row r="9" spans="1:11" ht="16.8" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
@@ -829,15 +829,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E9" s="19" t="str">
-        <f t="shared" ref="E9:E30" si="1">$E$4</f>
-        <v>לא נמכר</v>
+      <c r="E9" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="22">
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.75" customHeight="1">
+    <row r="10" spans="1:11" ht="16.8" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
@@ -858,7 +857,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.75" customHeight="1">
+    <row r="11" spans="1:11" ht="16.8" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
@@ -879,7 +878,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.75" customHeight="1">
+    <row r="12" spans="1:11" ht="16.8" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
@@ -893,15 +892,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E12" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E12" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="F12" s="21">
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.75" customHeight="1">
+    <row r="13" spans="1:11" ht="16.8" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
@@ -915,15 +913,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E13" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E13" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F13" s="22">
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.75" customHeight="1">
+    <row r="14" spans="1:11" ht="16.8" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
@@ -937,15 +934,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E14" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E14" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="21">
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.75" customHeight="1">
+    <row r="15" spans="1:11" ht="16.8" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -966,7 +962,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.75" customHeight="1">
+    <row r="16" spans="1:11" ht="16.8" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>31</v>
       </c>
@@ -987,7 +983,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16.75" customHeight="1">
+    <row r="17" spans="1:6" ht="16.8" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
@@ -1001,15 +997,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E17" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E17" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="22">
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16.75" customHeight="1">
+    <row r="18" spans="1:6" ht="16.8" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -1030,7 +1025,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16.75" customHeight="1">
+    <row r="19" spans="1:6" ht="16.8" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
@@ -1044,15 +1039,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E19" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E19" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="22">
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16.75" customHeight="1">
+    <row r="20" spans="1:6" ht="16.8" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
@@ -1066,15 +1060,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E20" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E20" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F20" s="21">
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16.75" customHeight="1">
+    <row r="21" spans="1:6" ht="16.8" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>37</v>
       </c>
@@ -1088,15 +1081,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E21" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E21" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="F21" s="22">
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16.75" customHeight="1">
+    <row r="22" spans="1:6" ht="16.8" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
@@ -1117,7 +1109,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16.75" customHeight="1">
+    <row r="23" spans="1:6" ht="16.8" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
@@ -1138,7 +1130,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16.75" customHeight="1">
+    <row r="24" spans="1:6" ht="16.8" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>40</v>
       </c>
@@ -1159,7 +1151,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="16.75" customHeight="1">
+    <row r="25" spans="1:6" ht="16.8" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>41</v>
       </c>
@@ -1173,15 +1165,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E25" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E25" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F25" s="22">
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16.75" customHeight="1">
+    <row r="26" spans="1:6" ht="16.8" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>43</v>
       </c>
@@ -1202,7 +1193,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.75" customHeight="1">
+    <row r="27" spans="1:6" ht="16.8" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>45</v>
       </c>
@@ -1216,15 +1207,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E27" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E27" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F27" s="22">
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16.75" customHeight="1">
+    <row r="28" spans="1:6" ht="16.8" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>47</v>
       </c>
@@ -1238,15 +1228,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E28" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E28" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="F28" s="21">
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16.75" customHeight="1">
+    <row r="29" spans="1:6" ht="16.8" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>48</v>
       </c>
@@ -1260,15 +1249,14 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E29" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E29" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F29" s="22">
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16.75" customHeight="1">
+    <row r="30" spans="1:6" ht="16.8" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
@@ -1282,9 +1270,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E30" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E30" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="21">
         <v>260</v>
@@ -1295,7 +1282,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$K$5:$K$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/inventory/excel/רשימת_מכנסיים.xlsx
+++ b/assets/inventory/excel/רשימת_מכנסיים.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\נווה\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAE7371-CF38-45C2-9060-1B0D1B87B52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="1960" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="רשימת מכנסיים" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -188,7 +187,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -490,12 +489,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PantsTable" displayName="PantsTable" ref="A3:D30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D30">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="מספר מכנס"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="שם מכנס"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="מידה"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="תאריך" dataDxfId="0">
+    <tableColumn id="1" name="מספר מכנס"/>
+    <tableColumn id="2" name="שם מכנס"/>
+    <tableColumn id="3" name="מידה"/>
+    <tableColumn id="4" name="תאריך" dataDxfId="0">
       <calculatedColumnFormula>$K$2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -651,19 +650,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="12.59765625" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.58203125" customWidth="1"/>
+    <col min="6" max="6" width="9.9140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
@@ -681,7 +680,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.2" customHeight="1" thickTop="1">
+    <row r="3" spans="1:11" ht="19.25" customHeight="1" thickTop="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -701,7 +700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.8" customHeight="1">
+    <row r="4" spans="1:11" ht="16.75" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
@@ -716,7 +715,7 @@
         <v>46217</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="21">
         <v>250</v>
@@ -725,7 +724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.8" customHeight="1">
+    <row r="5" spans="1:11" ht="16.75" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -749,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.8" customHeight="1">
+    <row r="6" spans="1:11" ht="16.75" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
@@ -773,7 +772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.8" customHeight="1">
+    <row r="7" spans="1:11" ht="16.75" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -787,14 +786,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>13</v>
+      <c r="E7" s="19" t="str">
+        <f>$E$4</f>
+        <v>לא נמכר</v>
       </c>
       <c r="F7" s="22">
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.8" customHeight="1">
+    <row r="8" spans="1:11" ht="16.75" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -809,13 +809,13 @@
         <v>46217</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" s="21">
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.8" customHeight="1">
+    <row r="9" spans="1:11" ht="16.75" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
@@ -829,14 +829,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>10</v>
+      <c r="E9" s="19" t="str">
+        <f t="shared" ref="E9:E30" si="1">$E$4</f>
+        <v>לא נמכר</v>
       </c>
       <c r="F9" s="22">
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.8" customHeight="1">
+    <row r="10" spans="1:11" ht="16.75" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
@@ -857,7 +858,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.8" customHeight="1">
+    <row r="11" spans="1:11" ht="16.75" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
@@ -878,7 +879,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.8" customHeight="1">
+    <row r="12" spans="1:11" ht="16.75" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
@@ -892,14 +893,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>10</v>
+      <c r="E12" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F12" s="21">
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.8" customHeight="1">
+    <row r="13" spans="1:11" ht="16.75" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
@@ -913,14 +915,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E13" s="19" t="s">
-        <v>10</v>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F13" s="22">
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.8" customHeight="1">
+    <row r="14" spans="1:11" ht="16.75" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
@@ -934,14 +937,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>10</v>
+      <c r="E14" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F14" s="21">
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.8" customHeight="1">
+    <row r="15" spans="1:11" ht="16.75" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -962,7 +966,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.8" customHeight="1">
+    <row r="16" spans="1:11" ht="16.75" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>31</v>
       </c>
@@ -983,7 +987,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16.8" customHeight="1">
+    <row r="17" spans="1:6" ht="16.75" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
@@ -997,14 +1001,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>13</v>
+      <c r="E17" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F17" s="22">
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16.8" customHeight="1">
+    <row r="18" spans="1:6" ht="16.75" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1030,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16.8" customHeight="1">
+    <row r="19" spans="1:6" ht="16.75" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
@@ -1039,14 +1044,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>13</v>
+      <c r="E19" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F19" s="22">
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16.8" customHeight="1">
+    <row r="20" spans="1:6" ht="16.75" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
@@ -1060,14 +1066,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>13</v>
+      <c r="E20" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F20" s="21">
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16.8" customHeight="1">
+    <row r="21" spans="1:6" ht="16.75" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>37</v>
       </c>
@@ -1081,14 +1088,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>13</v>
+      <c r="E21" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F21" s="22">
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="16.8" customHeight="1">
+    <row r="22" spans="1:6" ht="16.75" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
@@ -1109,7 +1117,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16.8" customHeight="1">
+    <row r="23" spans="1:6" ht="16.75" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
@@ -1130,7 +1138,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16.8" customHeight="1">
+    <row r="24" spans="1:6" ht="16.75" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>40</v>
       </c>
@@ -1151,7 +1159,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="16.8" customHeight="1">
+    <row r="25" spans="1:6" ht="16.75" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>41</v>
       </c>
@@ -1165,14 +1173,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E25" s="19" t="s">
-        <v>10</v>
+      <c r="E25" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F25" s="22">
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16.8" customHeight="1">
+    <row r="26" spans="1:6" ht="16.75" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>43</v>
       </c>
@@ -1193,7 +1202,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.8" customHeight="1">
+    <row r="27" spans="1:6" ht="16.75" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>45</v>
       </c>
@@ -1207,14 +1216,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E27" s="19" t="s">
-        <v>10</v>
+      <c r="E27" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F27" s="22">
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16.8" customHeight="1">
+    <row r="28" spans="1:6" ht="16.75" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>47</v>
       </c>
@@ -1228,14 +1238,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E28" s="20" t="s">
-        <v>10</v>
+      <c r="E28" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F28" s="21">
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16.8" customHeight="1">
+    <row r="29" spans="1:6" ht="16.75" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>48</v>
       </c>
@@ -1249,14 +1260,15 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>10</v>
+      <c r="E29" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F29" s="22">
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16.8" customHeight="1">
+    <row r="30" spans="1:6" ht="16.75" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>49</v>
       </c>
@@ -1270,8 +1282,9 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E30" s="20" t="s">
-        <v>13</v>
+      <c r="E30" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>לא נמכר</v>
       </c>
       <c r="F30" s="21">
         <v>260</v>
@@ -1282,7 +1295,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30">
       <formula1>$K$5:$K$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/inventory/excel/רשימת_מכנסיים.xlsx
+++ b/assets/inventory/excel/רשימת_מכנסיים.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -715,7 +715,7 @@
         <v>46217</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" s="21">
         <v>250</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="E7" s="19" t="str">
         <f>$E$4</f>
-        <v>לא נמכר</v>
+        <v>נמכר</v>
       </c>
       <c r="F7" s="22">
         <v>240</v>
@@ -829,9 +829,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E9" s="19" t="str">
-        <f t="shared" ref="E9:E30" si="1">$E$4</f>
-        <v>לא נמכר</v>
+      <c r="E9" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="22">
         <v>250</v>
@@ -894,8 +893,8 @@
         <v>46217</v>
       </c>
       <c r="E12" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+        <f t="shared" ref="E9:E30" si="1">$E$4</f>
+        <v>נמכר</v>
       </c>
       <c r="F12" s="21">
         <v>240</v>
@@ -915,9 +914,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E13" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E13" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F13" s="22">
         <v>230</v>
@@ -937,9 +935,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E14" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E14" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="21">
         <v>270</v>
@@ -1003,7 +1000,7 @@
       </c>
       <c r="E17" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+        <v>נמכר</v>
       </c>
       <c r="F17" s="22">
         <v>260</v>
@@ -1046,7 +1043,7 @@
       </c>
       <c r="E19" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+        <v>נמכר</v>
       </c>
       <c r="F19" s="22">
         <v>230</v>
@@ -1068,7 +1065,7 @@
       </c>
       <c r="E20" s="20" t="str">
         <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+        <v>נמכר</v>
       </c>
       <c r="F20" s="21">
         <v>250</v>
@@ -1090,7 +1087,7 @@
       </c>
       <c r="E21" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+        <v>נמכר</v>
       </c>
       <c r="F21" s="22">
         <v>270</v>
@@ -1173,9 +1170,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E25" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E25" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F25" s="22">
         <v>240</v>
@@ -1216,9 +1212,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E27" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E27" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F27" s="22">
         <v>250</v>
@@ -1238,9 +1233,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E28" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E28" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="F28" s="21">
         <v>250</v>
@@ -1260,9 +1254,8 @@
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="E29" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+      <c r="E29" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="F29" s="22">
         <v>250</v>
@@ -1284,7 +1277,7 @@
       </c>
       <c r="E30" s="20" t="str">
         <f t="shared" si="1"/>
-        <v>לא נמכר</v>
+        <v>נמכר</v>
       </c>
       <c r="F30" s="21">
         <v>260</v>

--- a/assets/inventory/excel/רשימת_מכנסיים.xlsx
+++ b/assets/inventory/excel/רשימת_מכנסיים.xlsx
@@ -893,7 +893,7 @@
         <v>46217</v>
       </c>
       <c r="E12" s="20" t="str">
-        <f t="shared" ref="E9:E30" si="1">$E$4</f>
+        <f t="shared" ref="E12:E30" si="1">$E$4</f>
         <v>נמכר</v>
       </c>
       <c r="F12" s="21">
@@ -1213,7 +1213,7 @@
         <v>46217</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F27" s="22">
         <v>250</v>
